--- a/subjects_test.xlsx
+++ b/subjects_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\IPS\Session\Tools\scratch\exam_system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\IPS\Session\Tools\scratch\exam_seating_chart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D014D8-A65E-4F52-84BB-E0496721866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D2D26C-49C4-4B8A-8907-84294D0AE9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>I Yr</t>
   </si>
@@ -34,112 +34,88 @@
     <t>IV Yr</t>
   </si>
   <si>
-    <t>CS101</t>
-  </si>
-  <si>
-    <t>CS201</t>
-  </si>
-  <si>
-    <t>CS301</t>
-  </si>
-  <si>
-    <t>CS401</t>
-  </si>
-  <si>
-    <t>CS102</t>
-  </si>
-  <si>
-    <t>CS202</t>
-  </si>
-  <si>
-    <t>CS302</t>
-  </si>
-  <si>
-    <t>CS402</t>
-  </si>
-  <si>
-    <t>CS103</t>
-  </si>
-  <si>
-    <t>CS203</t>
-  </si>
-  <si>
-    <t>CS303</t>
-  </si>
-  <si>
-    <t>CS104</t>
-  </si>
-  <si>
-    <t>CS105</t>
-  </si>
-  <si>
-    <t>CS204</t>
-  </si>
-  <si>
-    <t>CS205</t>
-  </si>
-  <si>
-    <t>CS206</t>
-  </si>
-  <si>
-    <t>CS304</t>
-  </si>
-  <si>
-    <t>CS305</t>
-  </si>
-  <si>
-    <t>CS306</t>
-  </si>
-  <si>
-    <t>adasdas</t>
-  </si>
-  <si>
-    <t>dfsdfs</t>
-  </si>
-  <si>
-    <t>dfgdfgdf</t>
-  </si>
-  <si>
-    <t>sdfdfh</t>
-  </si>
-  <si>
-    <t>gjhjhj</t>
-  </si>
-  <si>
-    <t>rtytry</t>
-  </si>
-  <si>
-    <t>hdfhfgh</t>
-  </si>
-  <si>
-    <t>fghfgh</t>
-  </si>
-  <si>
-    <t>fffhfg</t>
-  </si>
-  <si>
-    <t>hfghfgh</t>
-  </si>
-  <si>
-    <t>fghfghfgh</t>
-  </si>
-  <si>
-    <t>fghfds</t>
-  </si>
-  <si>
-    <t>sss</t>
-  </si>
-  <si>
-    <t>deresrs</t>
-  </si>
-  <si>
-    <t>rsdrsr</t>
-  </si>
-  <si>
-    <t>serser</t>
-  </si>
-  <si>
-    <t>erserser</t>
+    <t xml:space="preserve"> BSC MA03 </t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>PCC CI011</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>PEC-CI04(A)</t>
+  </si>
+  <si>
+    <t>WMC</t>
+  </si>
+  <si>
+    <t>PCC CI04</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>PCC CI012</t>
+  </si>
+  <si>
+    <t>FAIML</t>
+  </si>
+  <si>
+    <t>PEC-CI05(A)</t>
+  </si>
+  <si>
+    <t>BIG DATA HADOOP</t>
+  </si>
+  <si>
+    <t>PCC CI05</t>
+  </si>
+  <si>
+    <t>ADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCC CI013 </t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>PCC CI06</t>
+  </si>
+  <si>
+    <t>OOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PEC CI01</t>
+  </si>
+  <si>
+    <t>NLP</t>
+  </si>
+  <si>
+    <t>HSMC-HS04</t>
+  </si>
+  <si>
+    <t>EPOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> HSMC HS06</t>
+  </si>
+  <si>
+    <t>BCOM</t>
+  </si>
+  <si>
+    <t>IFC-EC01</t>
+  </si>
+  <si>
+    <t>S&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOC MA01(A) </t>
+  </si>
+  <si>
+    <t>SA</t>
   </si>
 </sst>
 </file>
@@ -181,7 +157,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -503,130 +480,120 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
-        <v>38</v>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
-        <v>39</v>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
